--- a/mode_docx_gen/part/lvttoc/phar1/PHAR1.xlsx
+++ b/mode_docx_gen/part/lvttoc/phar1/PHAR1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\24. МТЗ Т2\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\www_obj\mode_docx_gen\part\lvttoc\phar1\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FC0291-FF84-4B89-B823-3935D9A47231}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26820" windowHeight="9060"/>
+    <workbookView xWindow="540" yWindow="2730" windowWidth="37515" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="93">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -290,12 +291,21 @@
   </si>
   <si>
     <t>Ток блокировки</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>Imax</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -336,7 +346,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -372,11 +382,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -385,9 +406,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -689,8 +713,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -702,7 +726,7 @@
     <col min="13" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -793,8 +817,11 @@
       <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="7" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>30</v>
       </c>
@@ -886,7 +913,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>30</v>
       </c>
@@ -978,7 +1005,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>30</v>
       </c>
@@ -1162,7 +1189,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>30</v>
       </c>
@@ -1254,7 +1281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
@@ -1346,7 +1373,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>45</v>
       </c>
@@ -1437,8 +1464,11 @@
       <c r="AD8" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="AE8" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="9" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
@@ -1529,8 +1559,11 @@
       <c r="AD9" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="AE9" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
-    <row r="10" spans="1:30" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>45</v>
       </c>
@@ -1623,7 +1656,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AD6">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD6">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1632,7 +1665,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
